--- a/www/terminologies/ASS-A13-TypeEvenement-FluxStandardise.xlsx
+++ b/www/terminologies/ASS-A13-TypeEvenement-FluxStandardise.xlsx
@@ -105,13 +105,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R254-TypeEvenement/FHIR/TRE-R254-TypeEvenement|20240329120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R254-TypeEvenement/FHIR/TRE-R254-TypeEvenement</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R255-FluxStandardise/FHIR/TRE-R255-FluxStandardise|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R255-FluxStandardise/FHIR/TRE-R255-FluxStandardise</t>
   </si>
   <si>
     <t>DOC</t>
